--- a/figures/lecture5/6345.0/634507b.xlsx
+++ b/figures/lecture5/6345.0/634507b.xlsx
@@ -17,62 +17,62 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2615009A">Data1!$E$1:$E$10,Data1!$E$11:$E$114</definedName>
-    <definedName name="A2615009A_Data">Data1!$E$11:$E$114</definedName>
-    <definedName name="A2615009A_Latest">Data1!$E$114</definedName>
-    <definedName name="A2615010K">Data1!$K$1:$K$10,Data1!$K$11:$K$114</definedName>
-    <definedName name="A2615010K_Data">Data1!$K$11:$K$114</definedName>
-    <definedName name="A2615010K_Latest">Data1!$K$114</definedName>
-    <definedName name="A2615011L">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$114</definedName>
-    <definedName name="A2615011L_Data">Data1!$Q$11:$Q$114</definedName>
-    <definedName name="A2615011L_Latest">Data1!$Q$114</definedName>
-    <definedName name="A2615579C">Data1!$G$1:$G$10,Data1!$G$11:$G$114</definedName>
-    <definedName name="A2615579C_Data">Data1!$G$11:$G$114</definedName>
-    <definedName name="A2615579C_Latest">Data1!$G$114</definedName>
-    <definedName name="A2615580L">Data1!$M$1:$M$10,Data1!$M$11:$M$114</definedName>
-    <definedName name="A2615580L_Data">Data1!$M$11:$M$114</definedName>
-    <definedName name="A2615580L_Latest">Data1!$M$114</definedName>
-    <definedName name="A2615581R">Data1!$S$1:$S$10,Data1!$S$11:$S$114</definedName>
-    <definedName name="A2615581R_Data">Data1!$S$11:$S$114</definedName>
-    <definedName name="A2615581R_Latest">Data1!$S$114</definedName>
-    <definedName name="A2615959F">Data1!$F$1:$F$10,Data1!$F$11:$F$114</definedName>
-    <definedName name="A2615959F_Data">Data1!$F$11:$F$114</definedName>
-    <definedName name="A2615959F_Latest">Data1!$F$114</definedName>
-    <definedName name="A2615960R">Data1!$L$1:$L$10,Data1!$L$11:$L$114</definedName>
-    <definedName name="A2615960R_Data">Data1!$L$11:$L$114</definedName>
-    <definedName name="A2615960R_Latest">Data1!$L$114</definedName>
-    <definedName name="A2615961T">Data1!$R$1:$R$10,Data1!$R$11:$R$114</definedName>
-    <definedName name="A2615961T_Data">Data1!$R$11:$R$114</definedName>
-    <definedName name="A2615961T_Latest">Data1!$R$114</definedName>
-    <definedName name="A2626979V">Data1!$B$1:$B$10,Data1!$B$11:$B$114</definedName>
-    <definedName name="A2626979V_Data">Data1!$B$11:$B$114</definedName>
-    <definedName name="A2626979V_Latest">Data1!$B$114</definedName>
-    <definedName name="A2626980C">Data1!$H$1:$H$10,Data1!$H$11:$H$114</definedName>
-    <definedName name="A2626980C_Data">Data1!$H$11:$H$114</definedName>
-    <definedName name="A2626980C_Latest">Data1!$H$114</definedName>
-    <definedName name="A2626981F">Data1!$N$1:$N$10,Data1!$N$11:$N$114</definedName>
-    <definedName name="A2626981F_Data">Data1!$N$11:$N$114</definedName>
-    <definedName name="A2626981F_Latest">Data1!$N$114</definedName>
-    <definedName name="A2627549L">Data1!$D$1:$D$10,Data1!$D$11:$D$114</definedName>
-    <definedName name="A2627549L_Data">Data1!$D$11:$D$114</definedName>
-    <definedName name="A2627549L_Latest">Data1!$D$114</definedName>
-    <definedName name="A2627550W">Data1!$J$1:$J$10,Data1!$J$11:$J$114</definedName>
-    <definedName name="A2627550W_Data">Data1!$J$11:$J$114</definedName>
-    <definedName name="A2627550W_Latest">Data1!$J$114</definedName>
-    <definedName name="A2627551X">Data1!$P$1:$P$10,Data1!$P$11:$P$114</definedName>
-    <definedName name="A2627551X_Data">Data1!$P$11:$P$114</definedName>
-    <definedName name="A2627551X_Latest">Data1!$P$114</definedName>
-    <definedName name="A2627929R">Data1!$C$1:$C$10,Data1!$C$11:$C$114</definedName>
-    <definedName name="A2627929R_Data">Data1!$C$11:$C$114</definedName>
-    <definedName name="A2627929R_Latest">Data1!$C$114</definedName>
-    <definedName name="A2627930X">Data1!$I$1:$I$10,Data1!$I$11:$I$114</definedName>
-    <definedName name="A2627930X_Data">Data1!$I$11:$I$114</definedName>
-    <definedName name="A2627930X_Latest">Data1!$I$114</definedName>
-    <definedName name="A2627931A">Data1!$O$1:$O$10,Data1!$O$11:$O$114</definedName>
-    <definedName name="A2627931A_Data">Data1!$O$11:$O$114</definedName>
-    <definedName name="A2627931A_Latest">Data1!$O$114</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$114</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$114</definedName>
+    <definedName name="A2615009A">Data1!$E$1:$E$10,Data1!$E$11:$E$124</definedName>
+    <definedName name="A2615009A_Data">Data1!$E$11:$E$124</definedName>
+    <definedName name="A2615009A_Latest">Data1!$E$124</definedName>
+    <definedName name="A2615010K">Data1!$K$1:$K$10,Data1!$K$11:$K$124</definedName>
+    <definedName name="A2615010K_Data">Data1!$K$11:$K$124</definedName>
+    <definedName name="A2615010K_Latest">Data1!$K$124</definedName>
+    <definedName name="A2615011L">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$124</definedName>
+    <definedName name="A2615011L_Data">Data1!$Q$11:$Q$124</definedName>
+    <definedName name="A2615011L_Latest">Data1!$Q$124</definedName>
+    <definedName name="A2615579C">Data1!$G$1:$G$10,Data1!$G$11:$G$124</definedName>
+    <definedName name="A2615579C_Data">Data1!$G$11:$G$124</definedName>
+    <definedName name="A2615579C_Latest">Data1!$G$124</definedName>
+    <definedName name="A2615580L">Data1!$M$1:$M$10,Data1!$M$11:$M$124</definedName>
+    <definedName name="A2615580L_Data">Data1!$M$11:$M$124</definedName>
+    <definedName name="A2615580L_Latest">Data1!$M$124</definedName>
+    <definedName name="A2615581R">Data1!$S$1:$S$10,Data1!$S$11:$S$124</definedName>
+    <definedName name="A2615581R_Data">Data1!$S$11:$S$124</definedName>
+    <definedName name="A2615581R_Latest">Data1!$S$124</definedName>
+    <definedName name="A2615959F">Data1!$F$1:$F$10,Data1!$F$11:$F$124</definedName>
+    <definedName name="A2615959F_Data">Data1!$F$11:$F$124</definedName>
+    <definedName name="A2615959F_Latest">Data1!$F$124</definedName>
+    <definedName name="A2615960R">Data1!$L$1:$L$10,Data1!$L$11:$L$124</definedName>
+    <definedName name="A2615960R_Data">Data1!$L$11:$L$124</definedName>
+    <definedName name="A2615960R_Latest">Data1!$L$124</definedName>
+    <definedName name="A2615961T">Data1!$R$1:$R$10,Data1!$R$11:$R$124</definedName>
+    <definedName name="A2615961T_Data">Data1!$R$11:$R$124</definedName>
+    <definedName name="A2615961T_Latest">Data1!$R$124</definedName>
+    <definedName name="A2626979V">Data1!$B$1:$B$10,Data1!$B$11:$B$124</definedName>
+    <definedName name="A2626979V_Data">Data1!$B$11:$B$124</definedName>
+    <definedName name="A2626979V_Latest">Data1!$B$124</definedName>
+    <definedName name="A2626980C">Data1!$H$1:$H$10,Data1!$H$11:$H$124</definedName>
+    <definedName name="A2626980C_Data">Data1!$H$11:$H$124</definedName>
+    <definedName name="A2626980C_Latest">Data1!$H$124</definedName>
+    <definedName name="A2626981F">Data1!$N$1:$N$10,Data1!$N$11:$N$124</definedName>
+    <definedName name="A2626981F_Data">Data1!$N$11:$N$124</definedName>
+    <definedName name="A2626981F_Latest">Data1!$N$124</definedName>
+    <definedName name="A2627549L">Data1!$D$1:$D$10,Data1!$D$11:$D$124</definedName>
+    <definedName name="A2627549L_Data">Data1!$D$11:$D$124</definedName>
+    <definedName name="A2627549L_Latest">Data1!$D$124</definedName>
+    <definedName name="A2627550W">Data1!$J$1:$J$10,Data1!$J$11:$J$124</definedName>
+    <definedName name="A2627550W_Data">Data1!$J$11:$J$124</definedName>
+    <definedName name="A2627550W_Latest">Data1!$J$124</definedName>
+    <definedName name="A2627551X">Data1!$P$1:$P$10,Data1!$P$11:$P$124</definedName>
+    <definedName name="A2627551X_Data">Data1!$P$11:$P$124</definedName>
+    <definedName name="A2627551X_Latest">Data1!$P$124</definedName>
+    <definedName name="A2627929R">Data1!$C$1:$C$10,Data1!$C$11:$C$124</definedName>
+    <definedName name="A2627929R_Data">Data1!$C$11:$C$124</definedName>
+    <definedName name="A2627929R_Latest">Data1!$C$124</definedName>
+    <definedName name="A2627930X">Data1!$I$1:$I$10,Data1!$I$11:$I$124</definedName>
+    <definedName name="A2627930X_Data">Data1!$I$11:$I$124</definedName>
+    <definedName name="A2627930X_Latest">Data1!$I$124</definedName>
+    <definedName name="A2627931A">Data1!$O$1:$O$10,Data1!$O$11:$O$124</definedName>
+    <definedName name="A2627931A_Data">Data1!$O$11:$O$124</definedName>
+    <definedName name="A2627931A_Latest">Data1!$O$124</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$124</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$124</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1172,7 +1172,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2023</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -1853,10 +1853,10 @@
         <v>35674</v>
       </c>
       <c r="G12" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H12" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>27</v>
@@ -1885,10 +1885,10 @@
         <v>35674</v>
       </c>
       <c r="G13" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H13" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>27</v>
@@ -1917,10 +1917,10 @@
         <v>35674</v>
       </c>
       <c r="G14" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H14" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>27</v>
@@ -1949,10 +1949,10 @@
         <v>35674</v>
       </c>
       <c r="G15" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H15" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>27</v>
@@ -1981,10 +1981,10 @@
         <v>35674</v>
       </c>
       <c r="G16" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H16" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>27</v>
@@ -2013,10 +2013,10 @@
         <v>35674</v>
       </c>
       <c r="G17" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H17" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>27</v>
@@ -2045,10 +2045,10 @@
         <v>35674</v>
       </c>
       <c r="G18" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H18" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>37</v>
@@ -2077,10 +2077,10 @@
         <v>35674</v>
       </c>
       <c r="G19" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H19" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>37</v>
@@ -2109,10 +2109,10 @@
         <v>35674</v>
       </c>
       <c r="G20" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H20" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>37</v>
@@ -2141,10 +2141,10 @@
         <v>35674</v>
       </c>
       <c r="G21" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H21" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>37</v>
@@ -2173,10 +2173,10 @@
         <v>35674</v>
       </c>
       <c r="G22" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H22" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>37</v>
@@ -2205,10 +2205,10 @@
         <v>35674</v>
       </c>
       <c r="G23" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H23" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>37</v>
@@ -2237,10 +2237,10 @@
         <v>35674</v>
       </c>
       <c r="G24" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H24" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>37</v>
@@ -2269,10 +2269,10 @@
         <v>35674</v>
       </c>
       <c r="G25" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H25" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>37</v>
@@ -2301,10 +2301,10 @@
         <v>35674</v>
       </c>
       <c r="G26" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H26" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>37</v>
@@ -2333,10 +2333,10 @@
         <v>35674</v>
       </c>
       <c r="G27" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H27" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>37</v>
@@ -2365,10 +2365,10 @@
         <v>35674</v>
       </c>
       <c r="G28" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H28" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>37</v>
@@ -2397,10 +2397,10 @@
         <v>35674</v>
       </c>
       <c r="G29" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H29" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>37</v>
@@ -2453,7 +2453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S114"/>
+  <dimension ref="A1:S124"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -2874,58 +2874,58 @@
         <v>24</v>
       </c>
       <c r="B8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="C8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="D8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="E8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="F8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="G8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="I8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="J8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="K8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="L8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="M8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="N8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="O8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="P8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="Q8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="R8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="S8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -2933,58 +2933,58 @@
         <v>25</v>
       </c>
       <c r="B9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="M9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="O9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="P9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Q9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="R9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="S9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -9120,6 +9120,596 @@
       </c>
       <c r="S114" s="8">
         <v>3.7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A115" s="9">
+        <v>45170</v>
+      </c>
+      <c r="B115" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="C115" s="8">
+        <v>149</v>
+      </c>
+      <c r="D115" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="E115" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="F115" s="8">
+        <v>149</v>
+      </c>
+      <c r="G115" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="H115" s="8">
+        <v>2</v>
+      </c>
+      <c r="I115" s="8">
+        <v>1</v>
+      </c>
+      <c r="J115" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="K115" s="8">
+        <v>2</v>
+      </c>
+      <c r="L115" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="M115" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="N115" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="O115" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="P115" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q115" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="R115" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="S115" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A116" s="9">
+        <v>45261</v>
+      </c>
+      <c r="B116" s="8">
+        <v>150.69999999999999</v>
+      </c>
+      <c r="C116" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="D116" s="8">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="E116" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="F116" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="G116" s="8">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="H116" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="I116" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="J116" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="K116" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="L116" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="M116" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="N116" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O116" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="P116" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q116" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R116" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="S116" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A117" s="9">
+        <v>45352</v>
+      </c>
+      <c r="B117" s="8">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="C117" s="8">
+        <v>151.9</v>
+      </c>
+      <c r="D117" s="8">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="E117" s="8">
+        <v>152.1</v>
+      </c>
+      <c r="F117" s="8">
+        <v>152</v>
+      </c>
+      <c r="G117" s="8">
+        <v>152.1</v>
+      </c>
+      <c r="H117" s="8">
+        <v>1</v>
+      </c>
+      <c r="I117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J117" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="K117" s="8">
+        <v>1</v>
+      </c>
+      <c r="L117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M117" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="N117" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O117" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="P117" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="Q117" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R117" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="S117" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A118" s="9">
+        <v>45444</v>
+      </c>
+      <c r="B118" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="C118" s="8">
+        <v>152.9</v>
+      </c>
+      <c r="D118" s="8">
+        <v>152.6</v>
+      </c>
+      <c r="E118" s="8">
+        <v>152.4</v>
+      </c>
+      <c r="F118" s="8">
+        <v>153</v>
+      </c>
+      <c r="G118" s="8">
+        <v>152.6</v>
+      </c>
+      <c r="H118" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="I118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="J118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="K118" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="L118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="M118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="N118" s="8">
+        <v>4</v>
+      </c>
+      <c r="O118" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="P118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="Q118" s="8">
+        <v>4</v>
+      </c>
+      <c r="R118" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="S118" s="8">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A119" s="9">
+        <v>45536</v>
+      </c>
+      <c r="B119" s="8">
+        <v>155</v>
+      </c>
+      <c r="C119" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="D119" s="8">
+        <v>154.9</v>
+      </c>
+      <c r="E119" s="8">
+        <v>155</v>
+      </c>
+      <c r="F119" s="8">
+        <v>154.4</v>
+      </c>
+      <c r="G119" s="8">
+        <v>154.9</v>
+      </c>
+      <c r="H119" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="I119" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="J119" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K119" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="L119" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="M119" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="N119" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="O119" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="P119" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="Q119" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="R119" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="S119" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A120" s="9">
+        <v>45627</v>
+      </c>
+      <c r="B120" s="8">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="C120" s="8">
+        <v>155.5</v>
+      </c>
+      <c r="D120" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="E120" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="F120" s="8">
+        <v>155.5</v>
+      </c>
+      <c r="G120" s="8">
+        <v>156</v>
+      </c>
+      <c r="H120" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I120" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="J120" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="K120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="L120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="M120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="N120" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="O120" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="P120" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="Q120" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="R120" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="S120" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A121" s="9">
+        <v>45717</v>
+      </c>
+      <c r="B121" s="8">
+        <v>157.5</v>
+      </c>
+      <c r="C121" s="8">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="D121" s="8">
+        <v>157.5</v>
+      </c>
+      <c r="E121" s="8">
+        <v>157.4</v>
+      </c>
+      <c r="F121" s="8">
+        <v>157.4</v>
+      </c>
+      <c r="G121" s="8">
+        <v>157.5</v>
+      </c>
+      <c r="H121" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I121" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J121" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="K121" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="L121" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="M121" s="8">
+        <v>1</v>
+      </c>
+      <c r="N121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="O121" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="P121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="Q121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="R121" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="S121" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A122" s="9">
+        <v>45809</v>
+      </c>
+      <c r="B122" s="8">
+        <v>158.1</v>
+      </c>
+      <c r="C122" s="8">
+        <v>158.4</v>
+      </c>
+      <c r="D122" s="8">
+        <v>158.19999999999999</v>
+      </c>
+      <c r="E122" s="8">
+        <v>158</v>
+      </c>
+      <c r="F122" s="8">
+        <v>158.5</v>
+      </c>
+      <c r="G122" s="8">
+        <v>158.19999999999999</v>
+      </c>
+      <c r="H122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="I122" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="J122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="K122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="L122" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="M122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="N122" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="O122" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="P122" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="Q122" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="R122" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="S122" s="8">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A123" s="9">
+        <v>45901</v>
+      </c>
+      <c r="B123" s="8">
+        <v>160.9</v>
+      </c>
+      <c r="C123" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="D123" s="8">
+        <v>160.80000000000001</v>
+      </c>
+      <c r="E123" s="8">
+        <v>160.80000000000001</v>
+      </c>
+      <c r="F123" s="8">
+        <v>160.19999999999999</v>
+      </c>
+      <c r="G123" s="8">
+        <v>160.69999999999999</v>
+      </c>
+      <c r="H123" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="I123" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J123" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="K123" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="L123" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M123" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="N123" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="O123" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="P123" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="Q123" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="R123" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="S123" s="8">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A124" s="9">
+        <v>45992</v>
+      </c>
+      <c r="B124" s="8">
+        <v>161.30000000000001</v>
+      </c>
+      <c r="C124" s="8">
+        <v>161.6</v>
+      </c>
+      <c r="D124" s="8">
+        <v>161.4</v>
+      </c>
+      <c r="E124" s="8">
+        <v>161.19999999999999</v>
+      </c>
+      <c r="F124" s="8">
+        <v>161.69999999999999</v>
+      </c>
+      <c r="G124" s="8">
+        <v>161.4</v>
+      </c>
+      <c r="H124" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="I124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="J124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="K124" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="L124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="M124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="N124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="O124" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="P124" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="Q124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="R124" s="8">
+        <v>4</v>
+      </c>
+      <c r="S124" s="8">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
